--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T15:12:31+00:00</t>
+    <t>2026-03-18T14:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T14:24:59+00:00</t>
+    <t>2026-03-31T06:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T06:24:20+00:00</t>
+    <t>2026-04-09T04:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T04:48:36+00:00</t>
+    <t>2026-04-15T07:47:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:47:05+00:00</t>
+    <t>2026-04-15T19:05:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T19:05:31+00:00</t>
+    <t>2026-04-16T05:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onconova-aneuploid-score.xlsx
+++ b/StructureDefinition-onconova-aneuploid-score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T05:59:15+00:00</t>
+    <t>2026-04-26T18:09:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
